--- a/artfynd/A 540-2026 artfynd.xlsx
+++ b/artfynd/A 540-2026 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103690183</v>
+        <v>103690176</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380910.8771538151</v>
+        <v>381071</v>
       </c>
       <c r="R2" t="n">
-        <v>6779079.86075711</v>
+        <v>6779303</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,12 +775,7 @@
         <v>103690179</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380736.6074859046</v>
+        <v>380736</v>
       </c>
       <c r="R3" t="n">
-        <v>6779210.499029829</v>
+        <v>6779210</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103690182</v>
+        <v>103690178</v>
       </c>
       <c r="B4" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380910.8771538151</v>
+        <v>380853</v>
       </c>
       <c r="R4" t="n">
-        <v>6779079.86075711</v>
+        <v>6779313</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103690175</v>
+        <v>103690181</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>381070.9755337427</v>
+        <v>380893</v>
       </c>
       <c r="R5" t="n">
-        <v>6779303.623903656</v>
+        <v>6779089</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-11</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103690184</v>
+        <v>103690177</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>380932.2788599787</v>
+        <v>381030</v>
       </c>
       <c r="R6" t="n">
-        <v>6779053.994988404</v>
+        <v>6779348</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-11</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103690180</v>
+        <v>103690183</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>380787.1953038734</v>
+        <v>380911</v>
       </c>
       <c r="R7" t="n">
-        <v>6779159.953927148</v>
+        <v>6779080</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103690178</v>
+        <v>103690175</v>
       </c>
       <c r="B8" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380853.3856244888</v>
+        <v>381071</v>
       </c>
       <c r="R8" t="n">
-        <v>6779312.91205187</v>
+        <v>6779303</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103690181</v>
+        <v>103690180</v>
       </c>
       <c r="B9" t="n">
-        <v>90841</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>380892.7901510092</v>
+        <v>380787</v>
       </c>
       <c r="R9" t="n">
-        <v>6779089.175376402</v>
+        <v>6779160</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-09-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,37 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103690177</v>
+        <v>103690184</v>
       </c>
       <c r="B10" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>381029.8636632968</v>
+        <v>380933</v>
       </c>
       <c r="R10" t="n">
-        <v>6779348.041049856</v>
+        <v>6779054</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-09-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103690176</v>
+        <v>103690182</v>
       </c>
       <c r="B11" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>381070.9755337427</v>
+        <v>380911</v>
       </c>
       <c r="R11" t="n">
-        <v>6779303.623903656</v>
+        <v>6779080</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1616,9 @@
           <t>2021-08-24</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-09-11</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 540-2026 artfynd.xlsx
+++ b/artfynd/A 540-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103690176</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103690179</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103690178</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103690181</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103690177</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103690183</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103690175</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103690180</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103690184</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,8 +1692,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103690182</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>